--- a/data/trans_orig/P19E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2016</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2016 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142493</t>
+          <t>145298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184639</t>
+          <t>185345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176527</t>
+          <t>176548</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213782</t>
+          <t>213415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330673</t>
+          <t>331500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385588</t>
+          <t>384275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120872</t>
+          <t>120047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160434</t>
+          <t>159881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116429</t>
+          <t>117479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152472</t>
+          <t>154322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246929</t>
+          <t>250091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>304689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73774</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107924</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60824</t>
+          <t>59704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115194</t>
+          <t>118256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158160</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189596</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>238669</t>
+          <t>237800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>250760</t>
+          <t>250444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>296816</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>453831</t>
+          <t>455367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>522814</t>
+          <t>525376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181332</t>
+          <t>181577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226213</t>
+          <t>228026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163064</t>
+          <t>163663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>205856</t>
+          <t>206264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354506</t>
+          <t>355240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>418357</t>
+          <t>418826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108064</t>
+          <t>107999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151496</t>
+          <t>148431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>75900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107940</t>
+          <t>109747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194600</t>
+          <t>192186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>246363</t>
+          <t>245757</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>41888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48499</t>
+          <t>46645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231178</t>
+          <t>231731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>283250</t>
+          <t>281483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292080</t>
+          <t>292797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>341813</t>
+          <t>342549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>538578</t>
+          <t>540010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>609825</t>
+          <t>610682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183844</t>
+          <t>184849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231410</t>
+          <t>233463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193423</t>
+          <t>195190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>241374</t>
+          <t>241843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,47 +2258,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>30,01%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>37,18%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>425579</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>389325</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>460755</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>32,51%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>29,74%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>37,11%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>425579</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>393493</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>460934</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125096</t>
+          <t>126398</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167454</t>
+          <t>168288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94049</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132703</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224361</t>
+          <t>227385</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>285319</t>
+          <t>282892</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22370</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>25401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50087</t>
+          <t>50175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>54556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197360</t>
+          <t>197106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>247142</t>
+          <t>245697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255850</t>
+          <t>257373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310621</t>
+          <t>310795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>466316</t>
+          <t>470987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>540824</t>
+          <t>542767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162408</t>
+          <t>164395</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210324</t>
+          <t>210163</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195436</t>
+          <t>199184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>247383</t>
+          <t>246005</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>373191</t>
+          <t>376176</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>444924</t>
+          <t>442503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134478</t>
+          <t>135562</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>178292</t>
+          <t>180957</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97888</t>
+          <t>99076</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>139260</t>
+          <t>138578</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>246779</t>
+          <t>245344</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>304711</t>
+          <t>305678</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64392</t>
+          <t>65472</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>49883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85182</t>
+          <t>83462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140530</t>
+          <t>138596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>182007</t>
+          <t>182684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>158885</t>
+          <t>160030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208454</t>
+          <t>206569</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>313540</t>
+          <t>309060</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>374373</t>
+          <t>371812</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100436</t>
+          <t>100360</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138655</t>
+          <t>137391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>148103</t>
+          <t>149724</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>192366</t>
+          <t>194218</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>257446</t>
+          <t>256903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>317671</t>
+          <t>319486</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98950</t>
+          <t>99347</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138931</t>
+          <t>139007</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>78115</t>
+          <t>78268</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>115360</t>
+          <t>115015</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>188809</t>
+          <t>188362</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>241804</t>
+          <t>241750</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69303</t>
+          <t>67619</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>39302</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62565</t>
+          <t>62518</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98530</t>
+          <t>98412</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>72707</t>
+          <t>71356</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102780</t>
+          <t>103029</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>120404</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>159126</t>
+          <t>159383</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>201473</t>
+          <t>201123</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>251025</t>
+          <t>251937</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>66067</t>
+          <t>63976</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>97804</t>
+          <t>96416</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>94576</t>
+          <t>93765</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>132362</t>
+          <t>128399</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>169118</t>
+          <t>166144</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>217012</t>
+          <t>214890</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>80707</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>114776</t>
+          <t>115517</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60817</t>
+          <t>60361</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>92820</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>151639</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>198102</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>17465</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49153</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>44161</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35277</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43337</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>72311</t>
+          <t>72264</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>45857</t>
+          <t>46700</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>69412</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>90346</t>
+          <t>92660</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>132710</t>
+          <t>132651</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>147146</t>
+          <t>146244</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>194283</t>
+          <t>196805</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>67355</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>74771</t>
+          <t>75282</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>115749</t>
+          <t>114452</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>125483</t>
+          <t>127867</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>170818</t>
+          <t>172494</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>58898</t>
+          <t>58093</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>86072</t>
+          <t>84666</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>80562</t>
+          <t>83715</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>119046</t>
+          <t>123928</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>151708</t>
+          <t>148917</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>196593</t>
+          <t>198032</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>24592</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>51263</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>45171</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>78870</t>
+          <t>75137</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>28024</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>53934</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>54993</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>86571</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1103420</t>
+          <t>1100283</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1220728</t>
+          <t>1215794</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1442619</t>
+          <t>1440558</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1557325</t>
+          <t>1561363</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2579294</t>
+          <t>2571155</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2736284</t>
+          <t>2738379</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>933260</t>
+          <t>940335</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1041499</t>
+          <t>1044347</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1075837</t>
+          <t>1074833</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1188330</t>
+          <t>1187888</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2044205</t>
+          <t>2044869</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2197429</t>
+          <t>2189857</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>751812</t>
+          <t>756770</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>851831</t>
+          <t>857481</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>595021</t>
+          <t>598814</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>685391</t>
+          <t>688044</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1380698</t>
+          <t>1375725</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1510638</t>
+          <t>1514181</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>79374</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>119243</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>47192</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>80113</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>137078</t>
+          <t>137526</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>188277</t>
+          <t>190446</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>215499</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>275557</t>
+          <t>274402</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>101276</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>147562</t>
+          <t>151579</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>331996</t>
+          <t>332526</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>405798</t>
+          <t>407114</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2023</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2023 (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93887</t>
+          <t>93697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158721</t>
+          <t>161934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96730</t>
+          <t>97358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144631</t>
+          <t>144349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205103</t>
+          <t>203629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284714</t>
+          <t>283804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208361</t>
+          <t>206784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275659</t>
+          <t>276699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143263</t>
+          <t>142414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>192598</t>
+          <t>191570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368190</t>
+          <t>368287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448644</t>
+          <t>450152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52189</t>
+          <t>53193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80211</t>
+          <t>76585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -6761,97 +6761,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8175</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2385</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8363</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>8031</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -6874,97 +6874,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8043</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1602</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9349</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>9175</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>9300</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59674</t>
+          <t>60165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100581</t>
+          <t>102942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>103546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>213677</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195400</t>
+          <t>191386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297611</t>
+          <t>297894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216035</t>
+          <t>216285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270970</t>
+          <t>268339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256456</t>
+          <t>254215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>384399</t>
+          <t>379525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>493327</t>
+          <t>489248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627718</t>
+          <t>640407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62546</t>
+          <t>63849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105052</t>
+          <t>107994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82349</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>135841</t>
+          <t>135871</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25176</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38277</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129177</t>
+          <t>127816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172931</t>
+          <t>172079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180398</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>215637</t>
+          <t>215304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320797</t>
+          <t>319554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377483</t>
+          <t>377559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254518</t>
+          <t>250574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302403</t>
+          <t>299910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>266087</t>
+          <t>267342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>304955</t>
+          <t>306931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>534999</t>
+          <t>532452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>592456</t>
+          <t>591796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,86%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74672</t>
+          <t>75255</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110385</t>
+          <t>112056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>43657</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66395</t>
+          <t>66591</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124837</t>
+          <t>124583</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168185</t>
+          <t>167959</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183812</t>
+          <t>178400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>661858</t>
+          <t>668956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>231208</t>
+          <t>229279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>328259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>447950</t>
+          <t>448203</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1041973</t>
+          <t>1013254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144806</t>
+          <t>143714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472926</t>
+          <t>478064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301975</t>
+          <t>301971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383128</t>
+          <t>382943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>402534</t>
+          <t>422263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>837346</t>
+          <t>831219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60493</t>
+          <t>55290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204175</t>
+          <t>204375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66778</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95776</t>
+          <t>96507</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>130729</t>
+          <t>129389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>275021</t>
+          <t>273020</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43702</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99925</t>
+          <t>100774</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>136106</t>
+          <t>136546</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>148255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179594</t>
+          <t>180474</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>259146</t>
+          <t>258488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>307354</t>
+          <t>308448</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>241700</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>288813</t>
+          <t>288701</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>275150</t>
+          <t>273925</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>308601</t>
+          <t>308568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>529806</t>
+          <t>530429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>584432</t>
+          <t>587724</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>129207</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>168006</t>
+          <t>167912</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66966</t>
+          <t>66426</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>91053</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>201867</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>247836</t>
+          <t>250147</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,82 +9617,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>10116</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>24948</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>17052</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>34794</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>5757</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>10113</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>24948</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>17230</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>36061</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>77807</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>43282</t>
+          <t>38974</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>175629</t>
+          <t>176713</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>97689</t>
+          <t>93117</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>233416</t>
+          <t>233931</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>165580</t>
+          <t>164342</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>195959</t>
+          <t>196607</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>295920</t>
+          <t>293959</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>529190</t>
+          <t>539106</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>473623</t>
+          <t>472501</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>765235</t>
+          <t>775593</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>80626</t>
+          <t>79037</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>106887</t>
+          <t>106360</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27515</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>114430</t>
+          <t>114903</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>86054</t>
+          <t>83579</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>217143</t>
+          <t>216805</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>27163</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20374</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>48656</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53080</t>
+          <t>53688</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>73684</t>
+          <t>73842</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>89026</t>
+          <t>88855</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>115933</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>100812</t>
+          <t>101156</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>126479</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>166870</t>
+          <t>167738</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>194603</t>
+          <t>194944</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>276136</t>
+          <t>273349</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>314393</t>
+          <t>311393</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>77317</t>
+          <t>78081</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>101784</t>
+          <t>101612</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>103516</t>
+          <t>103002</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128581</t>
+          <t>128622</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>187040</t>
+          <t>188569</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>223436</t>
+          <t>223159</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -10853,12 +10853,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10868,12 +10868,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>29091</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>29722</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>46903</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10981,82 +10981,82 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>26459</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>41769</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>51396</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>42843</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>62633</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
           <t>9,09%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>33595</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>26744</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>41721</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>51396</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>42127</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>61104</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>751747</t>
+          <t>751121</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1482760</t>
+          <t>1485227</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>899231</t>
+          <t>887641</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1197213</t>
+          <t>1188041</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1818475</t>
+          <t>1826196</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2687501</t>
+          <t>2633255</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1654233</t>
+          <t>1654234</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1322834</t>
+          <t>1275541</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1803736</t>
+          <t>1798859</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1848675</t>
+          <t>1855371</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2301239</t>
+          <t>2298583</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3268681</t>
+          <t>3276998</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3926664</t>
+          <t>3911781</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>534860</t>
+          <t>522817</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>753854</t>
+          <t>755701</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>372497</t>
+          <t>362353</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>493686</t>
+          <t>493292</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>965977</t>
+          <t>987266</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1221945</t>
+          <t>1221534</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>68324</t>
+          <t>70028</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>104484</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>81219</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>127177</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>93088</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,47 +11698,47 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>183146</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>153818</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>211572</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>183146</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>156317</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>212659</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145298</t>
+          <t>142707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185345</t>
+          <t>183728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176548</t>
+          <t>176334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213415</t>
+          <t>213833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331500</t>
+          <t>329132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>384275</t>
+          <t>386176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120047</t>
+          <t>120759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159881</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117479</t>
+          <t>117091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154322</t>
+          <t>153257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250091</t>
+          <t>246716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>304689</t>
+          <t>303356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73758</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106386</t>
+          <t>109273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59704</t>
+          <t>60412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118256</t>
+          <t>115710</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>157809</t>
+          <t>158254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191829</t>
+          <t>191762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>237800</t>
+          <t>238432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>250444</t>
+          <t>252122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>294310</t>
+          <t>297044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>455367</t>
+          <t>453420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>525376</t>
+          <t>519768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181577</t>
+          <t>181239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>228026</t>
+          <t>227652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163663</t>
+          <t>163156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206264</t>
+          <t>205535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355240</t>
+          <t>352746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>418826</t>
+          <t>418988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107999</t>
+          <t>108783</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148431</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75900</t>
+          <t>75333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109747</t>
+          <t>108769</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>192186</t>
+          <t>189899</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>245757</t>
+          <t>243698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>46466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231731</t>
+          <t>232646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>281483</t>
+          <t>283502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292797</t>
+          <t>285651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342549</t>
+          <t>338494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>540010</t>
+          <t>537138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>610682</t>
+          <t>606435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184849</t>
+          <t>183945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233463</t>
+          <t>231064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195190</t>
+          <t>195184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>241843</t>
+          <t>244064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389325</t>
+          <t>391440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>460755</t>
+          <t>459925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126398</t>
+          <t>126189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168288</t>
+          <t>168516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90327</t>
+          <t>93993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128347</t>
+          <t>130889</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>227385</t>
+          <t>226255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282892</t>
+          <t>284523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50175</t>
+          <t>50801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54556</t>
+          <t>55610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197106</t>
+          <t>198264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245697</t>
+          <t>247608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>257373</t>
+          <t>258532</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310795</t>
+          <t>307545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>470987</t>
+          <t>467219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>542767</t>
+          <t>538204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164395</t>
+          <t>164790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210163</t>
+          <t>210500</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>199184</t>
+          <t>197711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246005</t>
+          <t>246032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>376176</t>
+          <t>371755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>442503</t>
+          <t>444246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>135562</t>
+          <t>135131</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180957</t>
+          <t>178753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99076</t>
+          <t>100290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138578</t>
+          <t>137755</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>245344</t>
+          <t>246582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>305678</t>
+          <t>305488</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>32109</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>65767</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49883</t>
+          <t>48235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83462</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138596</t>
+          <t>138584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>182684</t>
+          <t>182584</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>160030</t>
+          <t>157679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206569</t>
+          <t>203362</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>309060</t>
+          <t>307276</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>371812</t>
+          <t>369881</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100360</t>
+          <t>98333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137391</t>
+          <t>137888</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>149724</t>
+          <t>149020</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>194218</t>
+          <t>193839</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>256903</t>
+          <t>259464</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>319486</t>
+          <t>317127</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99347</t>
+          <t>99089</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>139007</t>
+          <t>140794</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>76428</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>115015</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>188362</t>
+          <t>187500</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>241750</t>
+          <t>241241</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67619</t>
+          <t>67810</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62518</t>
+          <t>64006</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98412</t>
+          <t>101036</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71356</t>
+          <t>72657</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>103029</t>
+          <t>104483</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>121557</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>159383</t>
+          <t>156545</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>201123</t>
+          <t>199655</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>251937</t>
+          <t>250870</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>63976</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>96416</t>
+          <t>96851</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>93765</t>
+          <t>95979</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>128399</t>
+          <t>131426</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>166144</t>
+          <t>170843</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>214890</t>
+          <t>218247</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>80707</t>
+          <t>79527</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>115517</t>
+          <t>114217</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60361</t>
+          <t>61415</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>92053</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>149415</t>
+          <t>151455</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>197011</t>
+          <t>200467</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>37101</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49054</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>44691</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>44139</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>72264</t>
+          <t>74325</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>46700</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,47 +4838,47 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>28,95%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>110828</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>91986</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>131621</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>29,26%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>110828</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>92660</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>132651</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>29,26%</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>146244</t>
+          <t>144871</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>196805</t>
+          <t>191450</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>45133</t>
+          <t>43954</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>67218</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>75282</t>
+          <t>75109</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>114452</t>
+          <t>113207</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>127867</t>
+          <t>126072</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>172494</t>
+          <t>171859</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>58093</t>
+          <t>59442</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>86356</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>83715</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>123928</t>
+          <t>122260</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>148917</t>
+          <t>147286</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>198032</t>
+          <t>197667</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>35300</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>49891</t>
+          <t>49694</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>75137</t>
+          <t>79710</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>41035</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>54624</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>54993</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>87615</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1100283</t>
+          <t>1110462</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1215794</t>
+          <t>1223826</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1440558</t>
+          <t>1446213</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1561363</t>
+          <t>1564130</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2571155</t>
+          <t>2572904</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2738379</t>
+          <t>2737292</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>940335</t>
+          <t>937875</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1044347</t>
+          <t>1038558</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1074833</t>
+          <t>1074389</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1187888</t>
+          <t>1185600</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2044869</t>
+          <t>2057948</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2189857</t>
+          <t>2211712</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>756770</t>
+          <t>754717</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>857481</t>
+          <t>855965</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>598814</t>
+          <t>594866</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>688044</t>
+          <t>684666</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1375725</t>
+          <t>1376762</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1514181</t>
+          <t>1517562</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>81382</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>120620</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>48552</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>81015</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>137526</t>
+          <t>134713</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>190446</t>
+          <t>189243</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>212137</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>274402</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>101276</t>
+          <t>100645</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>151579</t>
+          <t>146944</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>332526</t>
+          <t>329157</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>407114</t>
+          <t>402284</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -6417,32 +6417,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>124269</t>
+          <t>131037</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93697</t>
+          <t>100962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161934</t>
+          <t>162829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6452,32 +6452,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>119577</t>
+          <t>126456</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97358</t>
+          <t>103768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144349</t>
+          <t>154884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6487,32 +6487,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>243846</t>
+          <t>257493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203629</t>
+          <t>220467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283804</t>
+          <t>300306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -6530,32 +6530,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>242051</t>
+          <t>238546</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206784</t>
+          <t>207237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276699</t>
+          <t>271580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6565,32 +6565,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>167166</t>
+          <t>200111</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142414</t>
+          <t>172110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191570</t>
+          <t>223760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6600,32 +6600,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>409217</t>
+          <t>438657</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368287</t>
+          <t>396782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>450152</t>
+          <t>477499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -6643,32 +6643,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>57374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6678,32 +6678,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36763</t>
+          <t>52422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6713,32 +6713,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56137</t>
+          <t>70249</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>51006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76585</t>
+          <t>95135</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6982,17 +6982,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7017,17 +7017,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7052,17 +7052,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7099,32 +7099,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79878</t>
+          <t>104058</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60165</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102942</t>
+          <t>127661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7134,32 +7134,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>178277</t>
+          <t>194198</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103546</t>
+          <t>172397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213677</t>
+          <t>217624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7169,32 +7169,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>258155</t>
+          <t>298255</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191386</t>
+          <t>265100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297894</t>
+          <t>333151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -7212,32 +7212,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>241675</t>
+          <t>258860</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216285</t>
+          <t>232160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268339</t>
+          <t>286125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7247,32 +7247,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>296636</t>
+          <t>262276</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254215</t>
+          <t>239290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>379525</t>
+          <t>285645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>538311</t>
+          <t>521136</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489248</t>
+          <t>483121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640407</t>
+          <t>558671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7325,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84052</t>
+          <t>93380</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63849</t>
+          <t>71001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107994</t>
+          <t>117989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7360,32 +7360,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>43887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7395,32 +7395,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>108463</t>
+          <t>125595</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78895</t>
+          <t>101434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>135871</t>
+          <t>154126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7473,32 +7473,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7508,32 +7508,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7551,32 +7551,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7586,32 +7586,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19385</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7621,32 +7621,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>25691</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37860</t>
+          <t>39863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7664,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7699,17 +7699,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>149555</t>
+          <t>174967</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>127816</t>
+          <t>148654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172079</t>
+          <t>199243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7816,32 +7816,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>198090</t>
+          <t>226841</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>178580</t>
+          <t>206144</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>215304</t>
+          <t>247107</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7851,32 +7851,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>347645</t>
+          <t>401808</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>319554</t>
+          <t>371926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377559</t>
+          <t>436529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -7894,32 +7894,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>277291</t>
+          <t>322022</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250574</t>
+          <t>295846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299910</t>
+          <t>346989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7929,32 +7929,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>285188</t>
+          <t>327318</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>267342</t>
+          <t>307297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>306931</t>
+          <t>348892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7964,32 +7964,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>562480</t>
+          <t>649339</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>532452</t>
+          <t>617652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>591796</t>
+          <t>684108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -8007,32 +8007,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92061</t>
+          <t>105209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>87700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112056</t>
+          <t>125463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8042,32 +8042,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>61494</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43657</t>
+          <t>49746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66591</t>
+          <t>75238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8077,32 +8077,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>145899</t>
+          <t>166703</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124583</t>
+          <t>144534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167959</t>
+          <t>193153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -8120,102 +8120,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5481</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>4968</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11467</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1548</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>4525</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>10313</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -8233,32 +8233,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>25288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8268,32 +8268,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8303,32 +8303,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8346,17 +8346,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8381,17 +8381,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>542305</t>
+          <t>621378</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>542305</t>
+          <t>621378</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>542305</t>
+          <t>621378</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1078644</t>
+          <t>1242215</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1078644</t>
+          <t>1242215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1078644</t>
+          <t>1242215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>383636</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178400</t>
+          <t>134348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>668956</t>
+          <t>177383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>258953</t>
+          <t>249507</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229279</t>
+          <t>228830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>328259</t>
+          <t>271107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>642589</t>
+          <t>404562</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448203</t>
+          <t>376989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1013254</t>
+          <t>434613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>334016</t>
+          <t>367749</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>143714</t>
+          <t>343740</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>478064</t>
+          <t>395104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8611,32 +8611,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>355765</t>
+          <t>382129</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301971</t>
+          <t>359751</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382943</t>
+          <t>404455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8646,32 +8646,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>689782</t>
+          <t>749878</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>422263</t>
+          <t>716801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>831219</t>
+          <t>781014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -8689,32 +8689,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139148</t>
+          <t>144219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55290</t>
+          <t>124851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204375</t>
+          <t>167246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8724,32 +8724,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>81993</t>
+          <t>87596</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66052</t>
+          <t>73406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96507</t>
+          <t>103245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8759,32 +8759,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>221142</t>
+          <t>231815</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>207413</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>273020</t>
+          <t>259764</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -8802,32 +8802,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>19624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8837,32 +8837,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8872,32 +8872,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -8915,32 +8915,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8950,67 +8950,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>32924</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>23586</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>43874</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>31288</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>17539</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>45085</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>884735</t>
+          <t>697004</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>884735</t>
+          <t>697004</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>884735</t>
+          <t>697004</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9063,17 +9063,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>711359</t>
+          <t>735278</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>711359</t>
+          <t>735278</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>711359</t>
+          <t>735278</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9098,17 +9098,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1596095</t>
+          <t>1432282</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1596095</t>
+          <t>1432282</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1596095</t>
+          <t>1432282</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>118441</t>
+          <t>132701</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100774</t>
+          <t>112886</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>136546</t>
+          <t>153164</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>163630</t>
+          <t>186888</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148255</t>
+          <t>168981</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>180474</t>
+          <t>204953</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>282071</t>
+          <t>319589</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>258488</t>
+          <t>291420</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>308448</t>
+          <t>344771</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -9258,32 +9258,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>265595</t>
+          <t>292103</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>245146</t>
+          <t>271869</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>288701</t>
+          <t>319190</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9293,32 +9293,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>291865</t>
+          <t>323069</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>273925</t>
+          <t>303832</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>308568</t>
+          <t>341713</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9328,32 +9328,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>557460</t>
+          <t>615172</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>530429</t>
+          <t>583706</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>587724</t>
+          <t>644843</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -9371,32 +9371,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>147350</t>
+          <t>152436</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129207</t>
+          <t>131866</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>167912</t>
+          <t>171905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9406,32 +9406,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>78190</t>
+          <t>85274</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>72612</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91053</t>
+          <t>98287</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9441,32 +9441,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>225541</t>
+          <t>237710</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>201867</t>
+          <t>214635</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>250147</t>
+          <t>262579</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -9484,32 +9484,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9519,22 +9519,22 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9554,32 +9554,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -9597,32 +9597,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>36894</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9710,17 +9710,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>559371</t>
+          <t>606066</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>559371</t>
+          <t>606066</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>559371</t>
+          <t>606066</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9745,17 +9745,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>543113</t>
+          <t>605384</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>543113</t>
+          <t>605384</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>543113</t>
+          <t>605384</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9780,17 +9780,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1102485</t>
+          <t>1211450</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1102485</t>
+          <t>1211450</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1102485</t>
+          <t>1211450</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>75532</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>62195</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77807</t>
+          <t>88394</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>113089</t>
+          <t>123921</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38974</t>
+          <t>109264</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>176713</t>
+          <t>137389</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>178109</t>
+          <t>199453</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>93117</t>
+          <t>181912</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>233931</t>
+          <t>219932</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -9940,32 +9940,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>180488</t>
+          <t>201155</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>164342</t>
+          <t>184982</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>196607</t>
+          <t>218061</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9975,32 +9975,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>404205</t>
+          <t>218225</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>293959</t>
+          <t>202978</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>539106</t>
+          <t>232948</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10010,32 +10010,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>584693</t>
+          <t>419380</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>472501</t>
+          <t>395524</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>775593</t>
+          <t>442467</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -10053,32 +10053,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>93304</t>
+          <t>99323</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>79037</t>
+          <t>84115</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>106360</t>
+          <t>113331</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>76328</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>114903</t>
+          <t>87507</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>165748</t>
+          <t>175652</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>83579</t>
+          <t>156878</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>216805</t>
+          <t>193148</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -10166,32 +10166,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10201,32 +10201,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -10279,32 +10279,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28450</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10314,32 +10314,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>20374</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>31811</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>44941</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -10392,17 +10392,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>365989</t>
+          <t>404789</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>365989</t>
+          <t>404789</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>365989</t>
+          <t>404789</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>605580</t>
+          <t>435839</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>605580</t>
+          <t>435839</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>605580</t>
+          <t>435839</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>971569</t>
+          <t>840628</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>971569</t>
+          <t>840628</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>971569</t>
+          <t>840628</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>39062</t>
+          <t>43922</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30222</t>
+          <t>34528</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>48295</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>62862</t>
+          <t>71036</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53688</t>
+          <t>59553</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>73842</t>
+          <t>82940</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>101924</t>
+          <t>114959</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88855</t>
+          <t>99301</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>115933</t>
+          <t>131184</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -10622,32 +10622,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>113118</t>
+          <t>127399</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>101156</t>
+          <t>112702</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>126479</t>
+          <t>141412</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10657,32 +10657,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>180193</t>
+          <t>198365</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>167738</t>
+          <t>182462</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>194944</t>
+          <t>214111</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10692,32 +10692,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>325764</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>273349</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>311393</t>
+          <t>347186</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -10735,32 +10735,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>94405</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>78081</t>
+          <t>81558</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>101612</t>
+          <t>108690</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10770,32 +10770,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>115681</t>
+          <t>123308</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>103002</t>
+          <t>109928</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>137085</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10805,32 +10805,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>204810</t>
+          <t>217714</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>188569</t>
+          <t>199090</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>223159</t>
+          <t>237545</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -10848,32 +10848,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>25691</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10883,32 +10883,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10918,22 +10918,22 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>42099</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>29722</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>48084</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>41769</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>42843</t>
+          <t>43245</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>62633</t>
+          <t>63417</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -11074,17 +11074,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>275487</t>
+          <t>301746</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>275487</t>
+          <t>301746</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>275487</t>
+          <t>301746</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11109,17 +11109,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>413751</t>
+          <t>451173</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>413751</t>
+          <t>451173</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>413751</t>
+          <t>451173</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11144,17 +11144,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>689238</t>
+          <t>752919</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>689238</t>
+          <t>752919</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>689238</t>
+          <t>752919</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>959861</t>
+          <t>817272</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>751121</t>
+          <t>759590</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1485227</t>
+          <t>877719</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1094478</t>
+          <t>1178847</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>887641</t>
+          <t>1132618</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1188041</t>
+          <t>1231677</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2054339</t>
+          <t>1996119</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1826196</t>
+          <t>1921674</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2633255</t>
+          <t>2074178</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -11304,32 +11304,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1654234</t>
+          <t>1807833</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1275541</t>
+          <t>1744460</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1798859</t>
+          <t>1876095</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11339,32 +11339,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1981020</t>
+          <t>1911494</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1855371</t>
+          <t>1858606</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2298583</t>
+          <t>1964311</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11374,32 +11374,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3635254</t>
+          <t>3719327</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3276998</t>
+          <t>3627151</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3911781</t>
+          <t>3799616</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -11417,32 +11417,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>678711</t>
+          <t>727182</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>522817</t>
+          <t>680580</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>755701</t>
+          <t>783093</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11452,32 +11452,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>449028</t>
+          <t>498256</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>362353</t>
+          <t>464805</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>493292</t>
+          <t>537252</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11487,32 +11487,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1127740</t>
+          <t>1225438</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>987266</t>
+          <t>1166955</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1221534</t>
+          <t>1289285</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -11530,32 +11530,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>67206</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11565,32 +11565,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11600,32 +11600,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>85789</t>
+          <t>95628</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>78318</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>114251</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11643,32 +11643,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>126818</t>
+          <t>132598</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11678,32 +11678,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>67222</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>93088</t>
+          <t>94697</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11713,32 +11713,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>183146</t>
+          <t>191261</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>153818</t>
+          <t>167070</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>217230</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -11756,17 +11756,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11791,17 +11791,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -11826,17 +11826,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
